--- a/LLM_/My side/hospital_llm_detection_prompts.xlsx
+++ b/LLM_/My side/hospital_llm_detection_prompts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karan\Desktop\TK\TK\LLM_\My side\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A981D91C-35A8-449C-9F4E-497EB1D813C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F974657-7714-4CCA-879B-218A8101889B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
